--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127422548</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127422573</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98482</v>
+        <v>98484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127422548</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127422573</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98490</v>
+        <v>98493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127422548</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127422573</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127422548</v>
       </c>
       <c r="B5" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127422573</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127422294</v>
       </c>
       <c r="B2" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127422313</v>
       </c>
       <c r="B3" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127422294</v>
+        <v>127422573</v>
       </c>
       <c r="B2" t="n">
-        <v>100559</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjällådalen V om Tunbodarna, Mjällådalen V om Tunbodarna, Mpd</t>
+          <t>Mjällådalen N om Stor-Tunnäset, Mjällådalen N om Stor-Tunnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623552</v>
+        <v>623587</v>
       </c>
       <c r="R2" t="n">
-        <v>6952956</v>
+        <v>6952885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127422313</v>
+        <v>127422548</v>
       </c>
       <c r="B3" t="n">
-        <v>100559</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +791,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjällådalen V om Tunbodarna, Mjällådalen V om Tunbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623559</v>
+        <v>623596</v>
       </c>
       <c r="R3" t="n">
-        <v>6952987</v>
+        <v>6952894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +888,7 @@
         <v>127422213</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127422548</v>
+        <v>127422294</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +993,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mjällådalen V om Tunbodarna, Mjällådalen V om Tunbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623596</v>
+        <v>623552</v>
       </c>
       <c r="R5" t="n">
-        <v>6952894</v>
+        <v>6952956</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1082,7 @@
         <v>127422299</v>
       </c>
       <c r="B6" t="n">
-        <v>100559</v>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,53 +1176,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127422573</v>
+        <v>127422313</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>101228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mjällådalen N om Stor-Tunnäset, Mjällådalen N om Stor-Tunnäset, Mpd</t>
+          <t>Mjällådalen V om Tunbodarna, Mjällådalen V om Tunbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623587</v>
+        <v>623559</v>
       </c>
       <c r="R7" t="n">
-        <v>6952885</v>
+        <v>6952987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1270,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127422388</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mjällådalen V om Tunbodarna, Mjällådalen V om Tunbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>623539</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6952986</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28007-2023 artfynd.xlsx
+++ b/artfynd/A 28007-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422548</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422213</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422294</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422299</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422313</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,8 +1402,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422388</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>